--- a/models_data.xlsx
+++ b/models_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\coding\Coupled_Oscillators\JEB2026_Review_Ijspeert_Figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5878C566-C833-444B-9A24-E0049CDCB5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384451B7-624E-41CE-82FE-6DCAADF15A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="282">
   <si>
     <t>plot_label</t>
   </si>
@@ -379,6 +379,9 @@
     <t>Muscle-reflex finite-state/controller model with Hill-type muscle actuation.</t>
   </si>
   <si>
+    <t>Human 3D - Lee</t>
+  </si>
+  <si>
     <t>Scalable muscle-actuated human simulation</t>
   </si>
   <si>
@@ -567,6 +570,9 @@
     <t>3-D cat hindlimb model with finite-state/reflex rules and Ekeberg muscle models; irregular terrain/context = medium.</t>
   </si>
   <si>
+    <t>Mouse 3D</t>
+  </si>
+  <si>
     <t>Mouse</t>
   </si>
   <si>
@@ -591,6 +597,9 @@
     <t>Whole-body mouse musculoskeletal model; Table 1 high-DOF mouse entry, capped at 50+.</t>
   </si>
   <si>
+    <t>Human 3D - Rajagopal</t>
+  </si>
+  <si>
     <t>Full-body musculoskeletal model for muscle-driven simulation of gait</t>
   </si>
   <si>
@@ -621,9 +630,6 @@
     <t>Virtual Tadpole</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>Ferrario et al. 2021</t>
   </si>
   <si>
@@ -634,196 +640,243 @@
   </si>
   <si>
     <t>https://journals.plos.org/ploscompbiol/article?id=10.1371/journal.pcbi.1009654</t>
-  </si>
-  <si>
-    <t>Frog tadpole/Virtual Tadpole; HH controller; spring-damper actuation mapped to Ekeberg tick.</t>
-  </si>
-  <si>
-    <t>Mouse spinal-circuit gait model</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Danner et al. 2017</t>
-  </si>
-  <si>
-    <t>10.7554/eLife.31050</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.7554/eLife.31050</t>
-  </si>
-  <si>
-    <t>https://elifesciences.org/articles/31050</t>
-  </si>
-  <si>
-    <t>Controller-dominant spinal-circuit model; not a full-body neuromechanical model, but preserved from uploaded XLSX.</t>
-  </si>
-  <si>
-    <t>Insect-like hexapod robot</t>
-  </si>
-  <si>
-    <t>Versatile modular neural locomotion control</t>
-  </si>
-  <si>
-    <t>AMOS / modular hexapod</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Thor &amp; Manoonpong 2022</t>
-  </si>
-  <si>
-    <t>10.1038/s42256-022-00444-0</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1038/s42256-022-00444-0</t>
-  </si>
-  <si>
-    <t>https://www.nature.com/articles/s42256-022-00444-0</t>
-  </si>
-  <si>
-    <t>Physical hexapod neural-control work; preserves uploaded Poramate/hexapod entry.</t>
-  </si>
-  <si>
-    <t>ANYmal</t>
-  </si>
-  <si>
-    <t>Quadruped / animal-like robot</t>
-  </si>
-  <si>
-    <t>ANYmal harsh-environment quadruped</t>
-  </si>
-  <si>
-    <t>Torque control</t>
-  </si>
-  <si>
-    <t>Hutter et al. 2017</t>
-  </si>
-  <si>
-    <t>10.1080/01691864.2017.1378591</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1080/01691864.2017.1378591</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/doi/abs/10.1080/01691864.2017.1378591</t>
-  </si>
-  <si>
-    <t>ANYmal journal overview; torque-controlled quadruped platform in rough/harsh environments.</t>
-  </si>
-  <si>
-    <t>Axis</t>
-  </si>
-  <si>
-    <t>Tick / value</t>
-  </si>
-  <si>
-    <t>semantic coord.</t>
-  </si>
-  <si>
-    <t>plotted position</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Controller</t>
-  </si>
-  <si>
-    <t>Existing tick; no controller/passive models</t>
-  </si>
-  <si>
-    <t>Oscillators / FSM</t>
-  </si>
-  <si>
-    <t>FSM, open-loop, coupled oscillator</t>
-  </si>
-  <si>
-    <t>Leaky/rate/NN/RL mapped here; no extra controller tick</t>
-  </si>
-  <si>
-    <t>Actuator</t>
-  </si>
-  <si>
-    <t>Existing tick</t>
-  </si>
-  <si>
-    <t>DC motor / PD is mapped to Servomotor</t>
-  </si>
-  <si>
-    <t>Spring-damper mapped to Ekeberg; no extra tick</t>
-  </si>
-  <si>
-    <t>N DOF</t>
-  </si>
-  <si>
-    <t>Continuous axis</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Values &gt;= 50 cap here</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Intermediate non-tick value used in model table</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>How this workbook is used</t>
-  </si>
-  <si>
-    <t>The Models sheet is the source of truth for plot_figure_with_models_updated.py.</t>
-  </si>
-  <si>
-    <t>All entries from the uploaded XLSX are retained, and Table 1 entries from the Word file are included; Rajagopal et al. 2016 was added because it appears in the newer Table 1.</t>
-  </si>
-  <si>
-    <t>Controller and Actuator are discrete axes; the script snaps known categories to the listed tick coordinates.</t>
-  </si>
-  <si>
-    <t>N DOF remains continuous, so projections may fall between the labeled ticks.</t>
-  </si>
-  <si>
-    <t>When models share the same actuator and controller coordinates, the plot script offsets their Y/controller placement while keeping the projection connected to the original controller tick.</t>
-  </si>
-  <si>
-    <t>The plotting scripts use pandas.read_excel() to load this workbook.</t>
-  </si>
-  <si>
-    <t>Citation status is conservative: recent papers are marked as verified/influential or verified recent rather than incorrectly claiming they are highly cited already.</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>Xenopus</t>
-  </si>
-  <si>
-    <t>Mouse 3D</t>
-  </si>
-  <si>
-    <t>Human 3D - Rajagopal</t>
-  </si>
-  <si>
-    <t>Human 3D - Lee</t>
   </si>
   <si>
     <t>Mouse
 Danner</t>
+  </si>
+  <si>
+    <t>Mouse spinal-circuit gait model</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Danner et al. 2017</t>
+  </si>
+  <si>
+    <t>10.7554/eLife.31050</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.7554/eLife.31050</t>
+  </si>
+  <si>
+    <t>https://elifesciences.org/articles/31050</t>
+  </si>
+  <si>
+    <t>Controller-dominant spinal-circuit model; not a full-body neuromechanical model, but preserved from uploaded XLSX.</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>Insect-like hexapod robot</t>
+  </si>
+  <si>
+    <t>Versatile modular neural locomotion control</t>
+  </si>
+  <si>
+    <t>AMOS / modular hexapod</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Thor &amp; Manoonpong 2022</t>
+  </si>
+  <si>
+    <t>10.1038/s42256-022-00444-0</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s42256-022-00444-0</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s42256-022-00444-0</t>
+  </si>
+  <si>
+    <t>Physical hexapod neural-control work; preserves uploaded Poramate/hexapod entry.</t>
+  </si>
+  <si>
+    <t>ANYmal</t>
+  </si>
+  <si>
+    <t>Quadruped / animal-like robot</t>
+  </si>
+  <si>
+    <t>ANYmal harsh-environment quadruped</t>
+  </si>
+  <si>
+    <t>Torque control</t>
+  </si>
+  <si>
+    <t>Hutter et al. 2017</t>
+  </si>
+  <si>
+    <t>10.1080/01691864.2017.1378591</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/01691864.2017.1378591</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/abs/10.1080/01691864.2017.1378591</t>
+  </si>
+  <si>
+    <t>ANYmal journal overview; torque-controlled quadruped platform in rough/harsh environments.</t>
+  </si>
+  <si>
+    <t>Axis</t>
+  </si>
+  <si>
+    <t>Tick / value</t>
+  </si>
+  <si>
+    <t>semantic coord.</t>
+  </si>
+  <si>
+    <t>plotted position</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Existing tick; no controller/passive models</t>
+  </si>
+  <si>
+    <t>Oscillators / FSM</t>
+  </si>
+  <si>
+    <t>FSM, open-loop, coupled oscillator</t>
+  </si>
+  <si>
+    <t>Leaky/rate/NN/RL mapped here; no extra controller tick</t>
+  </si>
+  <si>
+    <t>Actuator</t>
+  </si>
+  <si>
+    <t>Existing tick</t>
+  </si>
+  <si>
+    <t>DC motor / PD is mapped to Servomotor</t>
+  </si>
+  <si>
+    <t>Spring-damper mapped to Ekeberg; no extra tick</t>
+  </si>
+  <si>
+    <t>N DOF</t>
+  </si>
+  <si>
+    <t>Continuous axis</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Values &gt;= 50 cap here</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Intermediate non-tick value used in model table</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>How this workbook is used</t>
+  </si>
+  <si>
+    <t>The Models sheet is the source of truth for plot_figure_with_models_updated.py.</t>
+  </si>
+  <si>
+    <t>All entries from the uploaded XLSX are retained, and Table 1 entries from the Word file are included; Rajagopal et al. 2016 was added because it appears in the newer Table 1.</t>
+  </si>
+  <si>
+    <t>Controller and Actuator are discrete axes; the script snaps known categories to the listed tick coordinates.</t>
+  </si>
+  <si>
+    <t>N DOF remains continuous, so projections may fall between the labeled ticks.</t>
+  </si>
+  <si>
+    <t>When models share the same actuator and controller coordinates, the plot script offsets their Y/controller placement while keeping the projection connected to the original controller tick.</t>
+  </si>
+  <si>
+    <t>The plotting scripts use pandas.read_excel() to load this workbook.</t>
+  </si>
+  <si>
+    <t>Citation status is conservative: recent papers are marked as verified/influential or verified recent rather than incorrectly claiming they are highly cited already.</t>
+  </si>
+  <si>
+    <t>Updated according to collaborator note. Ferrario et al. 2021 combines a high-complexity HH-type CNS model with a 3-D Virtual Tadpole body represented by 14,005 particles, elastic springs, segmented contractile muscle elements, and a high-complexity SPH water environment with approximately 2 million liquid particles. Plotted as high NN complexity, high N DOF (50+ endpoint), low-medium/spring-damper muscle complexity mapped to the Ekeberg tick, and high environment richness.</t>
+  </si>
+  <si>
+    <t>Lamprey
+Tytell</t>
+  </si>
+  <si>
+    <t>Closed-loop curvature-feedback lamprey swimming model</t>
+  </si>
+  <si>
+    <t>Hamlet et al. 2018</t>
+  </si>
+  <si>
+    <t>10.1371/journal.pcbi.1006324</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1371/journal.pcbi.1006324</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/ploscompbiol/article?id=10.1371/journal.pcbi.1006324</t>
+  </si>
+  <si>
+    <t>collaborator note / Tytell example</t>
+  </si>
+  <si>
+    <t>Added from collaborator note. Closed-loop lamprey model with chains of coupled phase oscillators, curvature sensory feedback, contractile muscle/body dynamics, and a high-fidelity fluid environment. The PLoS paper states that the surrounding fluid is simulated using a full Navier-Stokes model and that the midline/lateral filaments are finely discretized, so it is plotted as low controller complexity, medium muscle complexity, high N DOF, and high environment.</t>
+  </si>
+  <si>
+    <t>Biologically realistic human motion using joint torque actuation</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Jiang et al. 2019</t>
+  </si>
+  <si>
+    <t>10.1145/3306346.3322966</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3306346.3322966</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3306346.3322966</t>
+  </si>
+  <si>
+    <t>requested torque example</t>
+  </si>
+  <si>
+    <t>Re-added because the uploaded workbook did not contain the torque-actuation example from the previous step. Joint-torque actuation example using a 23-DOF OpenSim gait2392-derived human model; plotted at Torque control, 23 DOF, low/simple environment, and the existing neural/policy controller tick.</t>
+  </si>
+  <si>
+    <t>Human
+Torque</t>
+  </si>
+  <si>
+    <t>Xenopus</t>
   </si>
 </sst>
 </file>
@@ -906,7 +959,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ModelsTable" displayName="ModelsTable" ref="A1:AA22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ModelsTable" displayName="ModelsTable" ref="A1:AA24">
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="plot_label"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="animal"/>
@@ -954,7 +1007,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ReferenceChecksTable" displayName="ReferenceChecksTable" ref="A1:F22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ReferenceChecksTable" displayName="ReferenceChecksTable" ref="A1:F24">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="reference_short"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="doi"/>
@@ -1116,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1280,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>-0.78</v>
+        <v>-0.72</v>
       </c>
       <c r="S2" s="3">
         <v>0.2</v>
@@ -1361,7 +1414,7 @@
         <v>0.75</v>
       </c>
       <c r="R3" s="3">
-        <v>-0.72</v>
+        <v>-0.6</v>
       </c>
       <c r="S3" s="3">
         <v>0.18</v>
@@ -1879,13 +1932,13 @@
     </row>
     <row r="10" spans="1:27" ht="27.6">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
@@ -1931,22 +1984,22 @@
         <v>0.13</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>65</v>
@@ -1955,18 +2008,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="27.6">
       <c r="A11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
@@ -1982,7 +2035,7 @@
         <v>57</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J11" s="3">
         <v>1</v>
@@ -1994,10 +2047,10 @@
         <v>0.75</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O11" s="3">
         <v>0.94</v>
@@ -2015,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>40</v>
@@ -2036,21 +2089,21 @@
         <v>0.73799999999999999</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="27.6">
       <c r="A12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>30</v>
@@ -2077,16 +2130,16 @@
         <v>0.25</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O12" s="3">
         <v>0.16</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q12" s="3">
         <v>1</v>
@@ -2098,16 +2151,16 @@
         <v>0.2</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>85</v>
@@ -2119,21 +2172,21 @@
         <v>0.48200000000000004</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="27.6">
       <c r="A13" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>30</v>
@@ -2160,16 +2213,16 @@
         <v>0.25</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O13" s="3">
         <v>0.24</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q13" s="3">
         <v>0.5</v>
@@ -2181,16 +2234,16 @@
         <v>0.02</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X13" s="2" t="s">
         <v>40</v>
@@ -2202,21 +2255,21 @@
         <v>0.29800000000000004</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="27.6">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>30</v>
@@ -2243,16 +2296,16 @@
         <v>0.25</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O14" s="3">
         <v>0.12</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
@@ -2264,16 +2317,16 @@
         <v>0.22</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>40</v>
@@ -2285,21 +2338,21 @@
         <v>0.374</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="27.6">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>30</v>
@@ -2326,16 +2379,16 @@
         <v>0.25</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O15" s="3">
         <v>0.24</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q15" s="3">
         <v>0.5</v>
@@ -2347,16 +2400,16 @@
         <v>0</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>40</v>
@@ -2368,18 +2421,18 @@
         <v>0.39800000000000002</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="27.6">
       <c r="A16" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
@@ -2407,37 +2460,37 @@
         <v>0.75</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O16" s="3">
         <v>0.16</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q16" s="3">
         <v>0.5</v>
       </c>
       <c r="R16" s="3">
-        <v>0.13</v>
+        <v>-0.75</v>
       </c>
       <c r="S16" s="3">
         <v>0</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>40</v>
@@ -2449,18 +2502,18 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="27.6">
       <c r="A17" s="2" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
@@ -2509,19 +2562,19 @@
         <v>0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>65</v>
@@ -2530,18 +2583,18 @@
         <v>0.5</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="27.6">
       <c r="A18" s="2" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
@@ -2569,10 +2622,10 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O18" s="3">
         <v>0.74</v>
@@ -2590,39 +2643,39 @@
         <v>0</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Z18" s="3">
         <v>0.54800000000000004</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="27.6">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="82.8">
       <c r="A19" s="2" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
@@ -2638,7 +2691,7 @@
         <v>57</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J19" s="3">
         <v>1</v>
@@ -2650,19 +2703,19 @@
         <v>0.75</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>197</v>
+        <v>91</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>197</v>
+        <v>91</v>
       </c>
       <c r="O19" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R19" s="3">
         <v>-0.8</v>
@@ -2671,39 +2724,39 @@
         <v>0</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Z19" s="3">
-        <v>0.81</v>
+        <v>0.95</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>202</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="27.6">
       <c r="A20" s="2" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
@@ -2731,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -2752,19 +2805,19 @@
         <v>-0.18</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>41</v>
@@ -2773,21 +2826,21 @@
         <v>0.2</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="27.6">
       <c r="A21" s="2" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>30</v>
@@ -2814,16 +2867,16 @@
         <v>0.25</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O21" s="3">
         <v>0.36</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
@@ -2835,19 +2888,19 @@
         <v>0</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>41</v>
@@ -2856,21 +2909,21 @@
         <v>0.52200000000000002</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="27.6">
       <c r="A22" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>30</v>
@@ -2891,22 +2944,22 @@
         <v>0.5</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="L22" s="3">
         <v>0.5</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O22" s="3">
         <v>0.24</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
@@ -2918,16 +2971,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>40</v>
@@ -2939,7 +2992,169 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="69">
+      <c r="A23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O23" s="3">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-0.75</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="55.2">
+      <c r="A24" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-0.7</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0.39200000000000007</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -2947,7 +3162,7 @@
     <dataValidation type="list" sqref="E2:G22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H22" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" sqref="H2:H22" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"red,black"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2971,24 +3186,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
@@ -3000,15 +3215,15 @@
         <v>0.12</v>
       </c>
       <c r="E2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C3" s="4">
         <v>0.25</v>
@@ -3017,12 +3232,12 @@
         <v>0.315</v>
       </c>
       <c r="E3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -3034,12 +3249,12 @@
         <v>0.51</v>
       </c>
       <c r="E4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
@@ -3053,10 +3268,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -3067,7 +3282,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -3079,12 +3294,12 @@
         <v>0.12</v>
       </c>
       <c r="E7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -3096,15 +3311,15 @@
         <v>0.315</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C9" s="4">
         <v>0.5</v>
@@ -3115,7 +3330,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -3127,12 +3342,12 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B11" t="s">
         <v>110</v>
@@ -3146,10 +3361,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C12" s="4">
         <v>0</v>
@@ -3158,15 +3373,15 @@
         <v>0.12</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C13" s="4">
         <v>0.2</v>
@@ -3175,12 +3390,12 @@
         <v>0.27600000000000002</v>
       </c>
       <c r="E13" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B14" t="s">
         <v>47</v>
@@ -3192,15 +3407,15 @@
         <v>0.43200000000000005</v>
       </c>
       <c r="E14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C15" s="4">
         <v>0.6</v>
@@ -3209,15 +3424,15 @@
         <v>0.58799999999999997</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="C16" s="4">
         <v>0.8</v>
@@ -3226,12 +3441,12 @@
         <v>0.74400000000000011</v>
       </c>
       <c r="E16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
@@ -3243,15 +3458,15 @@
         <v>0.9</v>
       </c>
       <c r="E17" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C18" s="4">
         <v>0</v>
@@ -3262,7 +3477,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B19" t="s">
         <v>72</v>
@@ -3274,15 +3489,15 @@
         <v>0.27600000000000002</v>
       </c>
       <c r="E19" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="4">
         <v>0.5</v>
@@ -3293,7 +3508,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
         <v>48</v>
@@ -3305,15 +3520,15 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="E21" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C22" s="4">
         <v>1</v>
@@ -3332,7 +3547,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
@@ -3523,19 +3738,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F10" t="s">
         <v>65</v>
@@ -3543,16 +3758,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
@@ -3563,16 +3778,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
         <v>85</v>
@@ -3583,16 +3798,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s">
         <v>40</v>
@@ -3603,16 +3818,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
@@ -3623,16 +3838,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
@@ -3643,16 +3858,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
@@ -3663,19 +3878,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
         <v>65</v>
@@ -3683,39 +3898,39 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
         <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
         <v>65</v>
@@ -3723,19 +3938,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
@@ -3743,19 +3958,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D21" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F21" t="s">
         <v>41</v>
@@ -3763,22 +3978,62 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D22" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E22" t="s">
         <v>40</v>
       </c>
       <c r="F22" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="27.6">
+      <c r="A23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3799,42 +4054,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999">
       <c r="A1" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
